--- a/documents/Student Research Project - Gantt-Chart (no RACI) - Cao Đăng Khoa - UIT.xlsx
+++ b/documents/Student Research Project - Gantt-Chart (no RACI) - Cao Đăng Khoa - UIT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dkhoamac/Documents/Honours Project/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA1195E-4EE8-6B4F-AAC3-94E47293ECE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D39B7D-565C-424E-A489-B51C3840A74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17040" yWindow="620" windowWidth="10000" windowHeight="15380" xr2:uid="{7AEDD6EE-08B3-DF43-8C0E-E0ED61F366E0}"/>
+    <workbookView xWindow="820" yWindow="620" windowWidth="26220" windowHeight="15300" xr2:uid="{7AEDD6EE-08B3-DF43-8C0E-E0ED61F366E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t xml:space="preserve">PROJECT TITLE: Student research projects </t>
   </si>
@@ -219,9 +219,6 @@
     <t>STP8</t>
   </si>
   <si>
-    <t>Baseline design</t>
-  </si>
-  <si>
     <t>Realtime integration</t>
   </si>
   <si>
@@ -352,6 +349,18 @@
   </si>
   <si>
     <t>Final project design methods</t>
+  </si>
+  <si>
+    <t>Traditional method design</t>
+  </si>
+  <si>
+    <t>STP13</t>
+  </si>
+  <si>
+    <t>STP14</t>
+  </si>
+  <si>
+    <t>STP15</t>
   </si>
 </sst>
 </file>
@@ -1006,25 +1015,10 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="7" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="7" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1073,6 +1067,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="6" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="7" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1174,7 +1183,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="15" fmlaLink="$I$4" horiz="1" max="100" page="0" val="31"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="15" fmlaLink="$I$4" horiz="1" max="100" page="0" val="53"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1570,42 +1579,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:65" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
     </row>
     <row r="2" spans="2:65" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="2:65" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="50" t="s">
+      <c r="C3" s="44"/>
+      <c r="D3" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="50"/>
-      <c r="F3" s="51" t="s">
+      <c r="E3" s="45"/>
+      <c r="F3" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="51"/>
+      <c r="G3" s="46"/>
       <c r="H3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1614,376 +1623,376 @@
       </c>
     </row>
     <row r="4" spans="2:65" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="52">
+      <c r="B4" s="47">
         <v>45962</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="53">
+      <c r="C4" s="47"/>
+      <c r="D4" s="48">
         <v>46201</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="F4" s="54">
+      <c r="E4" s="48"/>
+      <c r="F4" s="49">
         <f ca="1">TODAY()</f>
-        <v>46119</v>
-      </c>
-      <c r="G4" s="54"/>
+        <v>46135</v>
+      </c>
+      <c r="G4" s="49"/>
       <c r="H4" s="3">
         <f ca="1">_xlfn.FLOOR.MATH(TODAY()-project_start)/7</f>
-        <v>22.428571428571427</v>
+        <v>24.714285714285715</v>
       </c>
       <c r="I4" s="3">
-        <v>31</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="2:65" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="59" t="s">
+      <c r="D5" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="61" t="s">
+      <c r="E5" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="43" t="s">
+      <c r="H5" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="45" t="s">
+      <c r="I5" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="58">
         <f>J6</f>
-        <v>46167</v>
-      </c>
-      <c r="K5" s="41"/>
-      <c r="L5" s="41"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="40">
+        <v>46321</v>
+      </c>
+      <c r="K5" s="59"/>
+      <c r="L5" s="59"/>
+      <c r="M5" s="59"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="60"/>
+      <c r="Q5" s="58">
         <f>Q6</f>
-        <v>46174</v>
-      </c>
-      <c r="R5" s="41"/>
-      <c r="S5" s="41"/>
-      <c r="T5" s="41"/>
-      <c r="U5" s="41"/>
-      <c r="V5" s="41"/>
-      <c r="W5" s="42"/>
-      <c r="X5" s="40">
+        <v>46328</v>
+      </c>
+      <c r="R5" s="59"/>
+      <c r="S5" s="59"/>
+      <c r="T5" s="59"/>
+      <c r="U5" s="59"/>
+      <c r="V5" s="59"/>
+      <c r="W5" s="60"/>
+      <c r="X5" s="58">
         <f>X6</f>
-        <v>46181</v>
-      </c>
-      <c r="Y5" s="41"/>
-      <c r="Z5" s="41"/>
-      <c r="AA5" s="41"/>
-      <c r="AB5" s="41"/>
-      <c r="AC5" s="41"/>
-      <c r="AD5" s="42"/>
-      <c r="AE5" s="40">
+        <v>46335</v>
+      </c>
+      <c r="Y5" s="59"/>
+      <c r="Z5" s="59"/>
+      <c r="AA5" s="59"/>
+      <c r="AB5" s="59"/>
+      <c r="AC5" s="59"/>
+      <c r="AD5" s="60"/>
+      <c r="AE5" s="58">
         <f>AE6</f>
-        <v>46188</v>
-      </c>
-      <c r="AF5" s="41"/>
-      <c r="AG5" s="41"/>
-      <c r="AH5" s="41"/>
-      <c r="AI5" s="41"/>
-      <c r="AJ5" s="41"/>
-      <c r="AK5" s="42"/>
-      <c r="AL5" s="40">
+        <v>46342</v>
+      </c>
+      <c r="AF5" s="59"/>
+      <c r="AG5" s="59"/>
+      <c r="AH5" s="59"/>
+      <c r="AI5" s="59"/>
+      <c r="AJ5" s="59"/>
+      <c r="AK5" s="60"/>
+      <c r="AL5" s="58">
         <f>AL6</f>
-        <v>46195</v>
-      </c>
-      <c r="AM5" s="41"/>
-      <c r="AN5" s="41"/>
-      <c r="AO5" s="41"/>
-      <c r="AP5" s="41"/>
-      <c r="AQ5" s="41"/>
-      <c r="AR5" s="42"/>
-      <c r="AS5" s="40">
+        <v>46349</v>
+      </c>
+      <c r="AM5" s="59"/>
+      <c r="AN5" s="59"/>
+      <c r="AO5" s="59"/>
+      <c r="AP5" s="59"/>
+      <c r="AQ5" s="59"/>
+      <c r="AR5" s="60"/>
+      <c r="AS5" s="58">
         <f>AS6</f>
-        <v>46202</v>
-      </c>
-      <c r="AT5" s="41"/>
-      <c r="AU5" s="41"/>
-      <c r="AV5" s="41"/>
-      <c r="AW5" s="41"/>
-      <c r="AX5" s="41"/>
-      <c r="AY5" s="42"/>
-      <c r="AZ5" s="40">
+        <v>46356</v>
+      </c>
+      <c r="AT5" s="59"/>
+      <c r="AU5" s="59"/>
+      <c r="AV5" s="59"/>
+      <c r="AW5" s="59"/>
+      <c r="AX5" s="59"/>
+      <c r="AY5" s="60"/>
+      <c r="AZ5" s="58">
         <f>AZ6</f>
-        <v>46209</v>
-      </c>
-      <c r="BA5" s="41"/>
-      <c r="BB5" s="41"/>
-      <c r="BC5" s="41"/>
-      <c r="BD5" s="41"/>
-      <c r="BE5" s="41"/>
-      <c r="BF5" s="42"/>
-      <c r="BG5" s="40">
+        <v>46363</v>
+      </c>
+      <c r="BA5" s="59"/>
+      <c r="BB5" s="59"/>
+      <c r="BC5" s="59"/>
+      <c r="BD5" s="59"/>
+      <c r="BE5" s="59"/>
+      <c r="BF5" s="60"/>
+      <c r="BG5" s="58">
         <f>BG6</f>
-        <v>46216</v>
-      </c>
-      <c r="BH5" s="41"/>
-      <c r="BI5" s="41"/>
-      <c r="BJ5" s="41"/>
-      <c r="BK5" s="41"/>
-      <c r="BL5" s="41"/>
-      <c r="BM5" s="42"/>
+        <v>46370</v>
+      </c>
+      <c r="BH5" s="59"/>
+      <c r="BI5" s="59"/>
+      <c r="BJ5" s="59"/>
+      <c r="BK5" s="59"/>
+      <c r="BL5" s="59"/>
+      <c r="BM5" s="60"/>
     </row>
     <row r="6" spans="2:65" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="55"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="45"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="61"/>
       <c r="J6" s="4">
         <f>$B$4-WEEKDAY(project_start,3)+(display_week-1)*7</f>
-        <v>46167</v>
+        <v>46321</v>
       </c>
       <c r="K6" s="5">
         <f>J6+1</f>
-        <v>46168</v>
+        <v>46322</v>
       </c>
       <c r="L6" s="5">
         <f t="shared" ref="L6:Q6" si="0">K6+1</f>
-        <v>46169</v>
+        <v>46323</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" si="0"/>
-        <v>46170</v>
+        <v>46324</v>
       </c>
       <c r="N6" s="5">
         <f t="shared" si="0"/>
-        <v>46171</v>
+        <v>46325</v>
       </c>
       <c r="O6" s="5">
         <f t="shared" si="0"/>
-        <v>46172</v>
+        <v>46326</v>
       </c>
       <c r="P6" s="5">
         <f t="shared" si="0"/>
-        <v>46173</v>
+        <v>46327</v>
       </c>
       <c r="Q6" s="5">
         <f t="shared" si="0"/>
-        <v>46174</v>
+        <v>46328</v>
       </c>
       <c r="R6" s="5">
         <f>Q6+1</f>
-        <v>46175</v>
+        <v>46329</v>
       </c>
       <c r="S6" s="5">
         <f t="shared" ref="S6:X6" si="1">R6+1</f>
-        <v>46176</v>
+        <v>46330</v>
       </c>
       <c r="T6" s="5">
         <f t="shared" si="1"/>
-        <v>46177</v>
+        <v>46331</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="1"/>
-        <v>46178</v>
+        <v>46332</v>
       </c>
       <c r="V6" s="5">
         <f t="shared" si="1"/>
-        <v>46179</v>
+        <v>46333</v>
       </c>
       <c r="W6" s="5">
         <f t="shared" si="1"/>
-        <v>46180</v>
+        <v>46334</v>
       </c>
       <c r="X6" s="5">
         <f t="shared" si="1"/>
-        <v>46181</v>
+        <v>46335</v>
       </c>
       <c r="Y6" s="5">
         <f>X6+1</f>
-        <v>46182</v>
+        <v>46336</v>
       </c>
       <c r="Z6" s="5">
         <f t="shared" ref="Z6:AE6" si="2">Y6+1</f>
-        <v>46183</v>
+        <v>46337</v>
       </c>
       <c r="AA6" s="5">
         <f t="shared" si="2"/>
-        <v>46184</v>
+        <v>46338</v>
       </c>
       <c r="AB6" s="5">
         <f t="shared" si="2"/>
-        <v>46185</v>
+        <v>46339</v>
       </c>
       <c r="AC6" s="5">
         <f t="shared" si="2"/>
-        <v>46186</v>
+        <v>46340</v>
       </c>
       <c r="AD6" s="5">
         <f t="shared" si="2"/>
-        <v>46187</v>
+        <v>46341</v>
       </c>
       <c r="AE6" s="5">
         <f t="shared" si="2"/>
-        <v>46188</v>
+        <v>46342</v>
       </c>
       <c r="AF6" s="5">
         <f>AE6+1</f>
-        <v>46189</v>
+        <v>46343</v>
       </c>
       <c r="AG6" s="5">
         <f t="shared" ref="AG6:BM6" si="3">AF6+1</f>
-        <v>46190</v>
+        <v>46344</v>
       </c>
       <c r="AH6" s="5">
         <f t="shared" si="3"/>
-        <v>46191</v>
+        <v>46345</v>
       </c>
       <c r="AI6" s="5">
         <f t="shared" si="3"/>
-        <v>46192</v>
+        <v>46346</v>
       </c>
       <c r="AJ6" s="5">
         <f t="shared" si="3"/>
-        <v>46193</v>
+        <v>46347</v>
       </c>
       <c r="AK6" s="5">
         <f t="shared" si="3"/>
-        <v>46194</v>
+        <v>46348</v>
       </c>
       <c r="AL6" s="5">
         <f t="shared" si="3"/>
-        <v>46195</v>
+        <v>46349</v>
       </c>
       <c r="AM6" s="5">
         <f t="shared" si="3"/>
-        <v>46196</v>
+        <v>46350</v>
       </c>
       <c r="AN6" s="5">
         <f t="shared" si="3"/>
-        <v>46197</v>
+        <v>46351</v>
       </c>
       <c r="AO6" s="5">
         <f t="shared" si="3"/>
-        <v>46198</v>
+        <v>46352</v>
       </c>
       <c r="AP6" s="5">
         <f t="shared" si="3"/>
-        <v>46199</v>
+        <v>46353</v>
       </c>
       <c r="AQ6" s="5">
         <f t="shared" si="3"/>
-        <v>46200</v>
+        <v>46354</v>
       </c>
       <c r="AR6" s="5">
         <f t="shared" si="3"/>
-        <v>46201</v>
+        <v>46355</v>
       </c>
       <c r="AS6" s="5">
         <f t="shared" si="3"/>
-        <v>46202</v>
+        <v>46356</v>
       </c>
       <c r="AT6" s="5">
         <f t="shared" si="3"/>
-        <v>46203</v>
+        <v>46357</v>
       </c>
       <c r="AU6" s="5">
         <f t="shared" si="3"/>
-        <v>46204</v>
+        <v>46358</v>
       </c>
       <c r="AV6" s="5">
         <f t="shared" si="3"/>
-        <v>46205</v>
+        <v>46359</v>
       </c>
       <c r="AW6" s="5">
         <f t="shared" si="3"/>
-        <v>46206</v>
+        <v>46360</v>
       </c>
       <c r="AX6" s="5">
         <f t="shared" si="3"/>
-        <v>46207</v>
+        <v>46361</v>
       </c>
       <c r="AY6" s="5">
         <f t="shared" si="3"/>
-        <v>46208</v>
+        <v>46362</v>
       </c>
       <c r="AZ6" s="5">
         <f t="shared" si="3"/>
-        <v>46209</v>
+        <v>46363</v>
       </c>
       <c r="BA6" s="5">
         <f t="shared" si="3"/>
-        <v>46210</v>
+        <v>46364</v>
       </c>
       <c r="BB6" s="5">
         <f t="shared" si="3"/>
-        <v>46211</v>
+        <v>46365</v>
       </c>
       <c r="BC6" s="5">
         <f t="shared" si="3"/>
-        <v>46212</v>
+        <v>46366</v>
       </c>
       <c r="BD6" s="5">
         <f t="shared" si="3"/>
-        <v>46213</v>
+        <v>46367</v>
       </c>
       <c r="BE6" s="5">
         <f t="shared" si="3"/>
-        <v>46214</v>
+        <v>46368</v>
       </c>
       <c r="BF6" s="5">
         <f t="shared" si="3"/>
-        <v>46215</v>
+        <v>46369</v>
       </c>
       <c r="BG6" s="5">
         <f t="shared" si="3"/>
-        <v>46216</v>
+        <v>46370</v>
       </c>
       <c r="BH6" s="5">
         <f t="shared" si="3"/>
-        <v>46217</v>
+        <v>46371</v>
       </c>
       <c r="BI6" s="5">
         <f t="shared" si="3"/>
-        <v>46218</v>
+        <v>46372</v>
       </c>
       <c r="BJ6" s="5">
         <f t="shared" si="3"/>
-        <v>46219</v>
+        <v>46373</v>
       </c>
       <c r="BK6" s="5">
         <f t="shared" si="3"/>
-        <v>46220</v>
+        <v>46374</v>
       </c>
       <c r="BL6" s="5">
         <f t="shared" si="3"/>
-        <v>46221</v>
+        <v>46375</v>
       </c>
       <c r="BM6" s="5">
         <f t="shared" si="3"/>
-        <v>46222</v>
+        <v>46376</v>
       </c>
     </row>
     <row r="7" spans="2:65" ht="20" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="56"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="46"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="62"/>
       <c r="J7" s="4" t="str">
         <f>LEFT(TEXT(J6,"ddd"),1)</f>
         <v>M</v>
@@ -2232,7 +2241,7 @@
       </c>
       <c r="H8" s="12" t="str">
         <f t="shared" ref="H8:H65" ca="1" si="12">IF(OR(D8="",E8=""),"",IF(TODAY()&gt;=D8,IF(TODAY()&lt;=E8,"In progress","Passed "&amp;TODAY()-E8&amp;"d"),"In "&amp;D8-TODAY()&amp;" days"))</f>
-        <v>Passed 148d</v>
+        <v>Passed 164d</v>
       </c>
       <c r="I8" s="13">
         <f ca="1">IF(H8="","",AVERAGE(I9:I13))</f>
@@ -2318,7 +2327,7 @@
       </c>
       <c r="H9" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 148d</v>
+        <v>Passed 164d</v>
       </c>
       <c r="I9" s="21">
         <v>1</v>
@@ -2404,7 +2413,7 @@
       </c>
       <c r="H10" s="20" t="str">
         <f t="shared" ref="H10:H11" ca="1" si="17">IF(OR(D10="",E10=""),"",IF(TODAY()&gt;=D10,IF(TODAY()&lt;=E10,"In progress","Passed "&amp;TODAY()-E10&amp;"d"),"In "&amp;D10-TODAY()&amp;" days"))</f>
-        <v>Passed 148d</v>
+        <v>Passed 164d</v>
       </c>
       <c r="I10" s="21">
         <v>1</v>
@@ -2490,7 +2499,7 @@
       </c>
       <c r="H11" s="20" t="str">
         <f t="shared" ca="1" si="17"/>
-        <v>Passed 148d</v>
+        <v>Passed 164d</v>
       </c>
       <c r="I11" s="21">
         <v>1</v>
@@ -2576,7 +2585,7 @@
       </c>
       <c r="H12" s="20" t="str">
         <f ca="1">IF(OR(D12="",E12=""),"",IF(TODAY()&gt;=D12,IF(TODAY()&lt;=E12,"In progress","Passed "&amp;TODAY()-E12&amp;"d"),"In "&amp;D12-TODAY()&amp;" days"))</f>
-        <v>Passed 148d</v>
+        <v>Passed 164d</v>
       </c>
       <c r="I12" s="21">
         <v>1</v>
@@ -2644,7 +2653,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D13" s="35">
         <v>45985</v>
@@ -2662,7 +2671,7 @@
       </c>
       <c r="H13" s="20" t="str">
         <f t="shared" ref="H13" ca="1" si="21">IF(OR(D13="",E13=""),"",IF(TODAY()&gt;=D13,IF(TODAY()&lt;=E13,"In progress","Passed "&amp;TODAY()-E13&amp;"d"),"In "&amp;D13-TODAY()&amp;" days"))</f>
-        <v>Passed 134d</v>
+        <v>Passed 150d</v>
       </c>
       <c r="I13" s="21">
         <v>1</v>
@@ -2747,7 +2756,7 @@
       </c>
       <c r="H14" s="12" t="str">
         <f ca="1">IF(OR(D14="",E14=""),"",IF(TODAY()&gt;=D14,IF(TODAY()&lt;=E14,"In progress","Passed "&amp;TODAY()-E14&amp;"d"),"In "&amp;D14-TODAY()&amp;" days"))</f>
-        <v>Passed 128d</v>
+        <v>Passed 144d</v>
       </c>
       <c r="I14" s="13">
         <f ca="1">IF(H14="","",AVERAGE(I15:I19))</f>
@@ -2833,7 +2842,7 @@
       </c>
       <c r="H15" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 128d</v>
+        <v>Passed 144d</v>
       </c>
       <c r="I15" s="21">
         <v>1</v>
@@ -2918,7 +2927,7 @@
       </c>
       <c r="H16" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 128d</v>
+        <v>Passed 144d</v>
       </c>
       <c r="I16" s="21">
         <v>1</v>
@@ -3003,7 +3012,7 @@
       </c>
       <c r="H17" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 128d</v>
+        <v>Passed 144d</v>
       </c>
       <c r="I17" s="21">
         <v>1</v>
@@ -3088,7 +3097,7 @@
       </c>
       <c r="H18" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 128d</v>
+        <v>Passed 144d</v>
       </c>
       <c r="I18" s="21">
         <v>1</v>
@@ -3173,7 +3182,7 @@
       </c>
       <c r="H19" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 128d</v>
+        <v>Passed 144d</v>
       </c>
       <c r="I19" s="21">
         <v>1</v>
@@ -3258,7 +3267,7 @@
       </c>
       <c r="H20" s="12" t="str">
         <f t="shared" ref="H20:H24" ca="1" si="22">IF(OR(D20="",E20=""),"",IF(TODAY()&gt;=D20,IF(TODAY()&lt;=E20,"In progress","Passed "&amp;TODAY()-E20&amp;"d"),"In "&amp;D20-TODAY()&amp;" days"))</f>
-        <v>Passed 121d</v>
+        <v>Passed 137d</v>
       </c>
       <c r="I20" s="13">
         <f ca="1">IF(H20="","",AVERAGE(I21:I24))</f>
@@ -3344,7 +3353,7 @@
       </c>
       <c r="H21" s="20" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>Passed 121d</v>
+        <v>Passed 137d</v>
       </c>
       <c r="I21" s="21">
         <v>1</v>
@@ -3430,7 +3439,7 @@
       </c>
       <c r="H22" s="20" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>Passed 121d</v>
+        <v>Passed 137d</v>
       </c>
       <c r="I22" s="21">
         <v>1</v>
@@ -3516,7 +3525,7 @@
       </c>
       <c r="H23" s="20" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>Passed 121d</v>
+        <v>Passed 137d</v>
       </c>
       <c r="I23" s="21">
         <v>1</v>
@@ -3602,7 +3611,7 @@
       </c>
       <c r="H24" s="20" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>Passed 121d</v>
+        <v>Passed 137d</v>
       </c>
       <c r="I24" s="21">
         <v>1</v>
@@ -3669,7 +3678,7 @@
         <v>40</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D25" s="37">
         <v>45998</v>
@@ -3687,7 +3696,7 @@
       </c>
       <c r="H25" s="32" t="str">
         <f ca="1">IF(OR(D25="",E25=""),"",IF(TODAY()&gt;=D25,IF(TODAY()&lt;=E25,"In progress","Passed "&amp;TODAY()-E25&amp;"d"),"In "&amp;D25-TODAY()&amp;" days"))</f>
-        <v>Passed 120d</v>
+        <v>Passed 136d</v>
       </c>
       <c r="I25" s="13">
         <f ca="1">IF(H25="","",AVERAGE(I26:I26))</f>
@@ -3755,7 +3764,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D26" s="34">
         <v>45998</v>
@@ -3773,7 +3782,7 @@
       </c>
       <c r="H26" s="20" t="str">
         <f t="shared" ref="H26" ca="1" si="27">IF(OR(D26="",E26=""),"",IF(TODAY()&gt;=D26,IF(TODAY()&lt;=E26,"In progress","Passed "&amp;TODAY()-E26&amp;"d"),"In "&amp;D26-TODAY()&amp;" days"))</f>
-        <v>Passed 120d</v>
+        <v>Passed 136d</v>
       </c>
       <c r="I26" s="21">
         <v>1</v>
@@ -3858,7 +3867,7 @@
       </c>
       <c r="H27" s="12" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 35d</v>
+        <v>Passed 51d</v>
       </c>
       <c r="I27" s="13">
         <f ca="1">IF(H27="","",AVERAGE(I28:I31))</f>
@@ -3944,7 +3953,7 @@
       </c>
       <c r="H28" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 35d</v>
+        <v>Passed 51d</v>
       </c>
       <c r="I28" s="21">
         <v>1</v>
@@ -4030,7 +4039,7 @@
       </c>
       <c r="H29" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 35d</v>
+        <v>Passed 51d</v>
       </c>
       <c r="I29" s="21">
         <v>1</v>
@@ -4116,7 +4125,7 @@
       </c>
       <c r="H30" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 35d</v>
+        <v>Passed 51d</v>
       </c>
       <c r="I30" s="21">
         <v>1</v>
@@ -4202,7 +4211,7 @@
       </c>
       <c r="H31" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 35d</v>
+        <v>Passed 51d</v>
       </c>
       <c r="I31" s="21">
         <v>1</v>
@@ -4269,7 +4278,7 @@
         <v>46</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D32" s="37">
         <v>46033</v>
@@ -4287,7 +4296,7 @@
       </c>
       <c r="H32" s="32" t="str">
         <f ca="1">IF(OR(D32="",E32=""),"",IF(TODAY()&gt;=D32,IF(TODAY()&lt;=E32,"In progress","Passed "&amp;TODAY()-E32&amp;"d"),"In "&amp;D32-TODAY()&amp;" days"))</f>
-        <v>Passed 85d</v>
+        <v>Passed 101d</v>
       </c>
       <c r="I32" s="13">
         <f ca="1">IF(H32="","",AVERAGE(I33:I33))</f>
@@ -4355,7 +4364,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D33" s="34">
         <v>46033</v>
@@ -4373,7 +4382,7 @@
       </c>
       <c r="H33" s="20" t="str">
         <f t="shared" ref="H33" ca="1" si="30">IF(OR(D33="",E33=""),"",IF(TODAY()&gt;=D33,IF(TODAY()&lt;=E33,"In progress","Passed "&amp;TODAY()-E33&amp;"d"),"In "&amp;D33-TODAY()&amp;" days"))</f>
-        <v>Passed 85d</v>
+        <v>Passed 101d</v>
       </c>
       <c r="I33" s="21">
         <v>1</v>
@@ -4440,7 +4449,7 @@
         <v>51</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D34" s="33">
         <v>46099</v>
@@ -4458,11 +4467,11 @@
       </c>
       <c r="H34" s="12" t="str">
         <f ca="1">IF(OR(D34="",E34=""),"",IF(TODAY()&gt;=D34,IF(TODAY()&lt;=E34,"In progress","Passed "&amp;TODAY()-E34&amp;"d"),"In "&amp;D34-TODAY()&amp;" days"))</f>
-        <v>Passed 9d</v>
+        <v>Passed 25d</v>
       </c>
       <c r="I34" s="13">
         <f ca="1">IF(H34="","",AVERAGE(I35:I39))</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J34" s="14"/>
       <c r="K34" s="15"/>
@@ -4789,7 +4798,7 @@
         <v/>
       </c>
       <c r="I38" s="21">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J38" s="22"/>
       <c r="K38" s="23"/>
@@ -4871,7 +4880,7 @@
         <v/>
       </c>
       <c r="I39" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="22"/>
       <c r="K39" s="22"/>
@@ -4935,7 +4944,7 @@
         <v>56</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D40" s="33">
         <v>46111</v>
@@ -4953,10 +4962,10 @@
       </c>
       <c r="H40" s="12" t="str">
         <f ca="1">IF(OR(D40="",E40=""),"",IF(TODAY()&gt;=D40,IF(TODAY()&lt;=E40,"In progress","Passed "&amp;TODAY()-E40&amp;"d"),"In "&amp;D40-TODAY()&amp;" days"))</f>
-        <v>In progress</v>
+        <v>Passed 10d</v>
       </c>
       <c r="I40" s="13">
-        <f ca="1">IF(H40="","",AVERAGE(I41:I57))</f>
+        <f ca="1">IF(H40="","",AVERAGE(I41:I45))</f>
         <v>0</v>
       </c>
       <c r="J40" s="14"/>
@@ -5185,7 +5194,7 @@
         <v>3</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D43" s="34"/>
       <c r="E43" s="35"/>
@@ -5427,10 +5436,10 @@
     </row>
     <row r="46" spans="2:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B46" s="28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D46" s="37">
         <v>46115</v>
@@ -5448,11 +5457,11 @@
       </c>
       <c r="H46" s="32" t="str">
         <f ca="1">IF(OR(D46="",E46=""),"",IF(TODAY()&gt;=D46,IF(TODAY()&lt;=E46,"In progress","Passed "&amp;TODAY()-E46&amp;"d"),"In "&amp;D46-TODAY()&amp;" days"))</f>
-        <v>Passed 1d</v>
+        <v>Passed 17d</v>
       </c>
       <c r="I46" s="13">
-        <f ca="1">IF(H46="","",AVERAGE(I51:I63))</f>
-        <v>0</v>
+        <f ca="1">IF(H46="","",AVERAGE(I47:I50))</f>
+        <v>1</v>
       </c>
       <c r="J46" s="14"/>
       <c r="K46" s="15"/>
@@ -5516,7 +5525,7 @@
         <v>1</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D47" s="34"/>
       <c r="E47" s="35"/>
@@ -5533,7 +5542,7 @@
         <v/>
       </c>
       <c r="I47" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" s="22"/>
       <c r="K47" s="23"/>
@@ -5598,7 +5607,7 @@
         <v>2</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D48" s="34"/>
       <c r="E48" s="35"/>
@@ -5615,7 +5624,7 @@
         <v/>
       </c>
       <c r="I48" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="22"/>
       <c r="K48" s="23"/>
@@ -5680,7 +5689,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D49" s="34"/>
       <c r="E49" s="35"/>
@@ -5697,7 +5706,7 @@
         <v/>
       </c>
       <c r="I49" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="22"/>
       <c r="K49" s="23"/>
@@ -5762,7 +5771,7 @@
         <v>4</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D50" s="34"/>
       <c r="E50" s="35"/>
@@ -5779,7 +5788,7 @@
         <v/>
       </c>
       <c r="I50" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="22"/>
       <c r="K50" s="23"/>
@@ -5840,10 +5849,10 @@
     </row>
     <row r="51" spans="2:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="8" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D51" s="33">
         <v>46125</v>
@@ -5861,11 +5870,11 @@
       </c>
       <c r="H51" s="12" t="str">
         <f ca="1">IF(OR(D51="",E51=""),"",IF(TODAY()&gt;=D51,IF(TODAY()&lt;=E51,"In progress","Passed "&amp;TODAY()-E51&amp;"d"),"In "&amp;D51-TODAY()&amp;" days"))</f>
-        <v>In 6 days</v>
+        <v>In progress</v>
       </c>
       <c r="I51" s="13">
-        <f ca="1">IF(H51="","",AVERAGE(I52:I64))</f>
-        <v>0</v>
+        <f ca="1">IF(H51="","",AVERAGE(I52:I55))</f>
+        <v>0.25</v>
       </c>
       <c r="J51" s="14"/>
       <c r="K51" s="15"/>
@@ -5946,7 +5955,7 @@
         <v/>
       </c>
       <c r="I52" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="22"/>
       <c r="K52" s="22"/>
@@ -6253,10 +6262,10 @@
     </row>
     <row r="56" spans="2:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="8" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="D56" s="33">
         <v>46147</v>
@@ -6274,11 +6283,10 @@
       </c>
       <c r="H56" s="12" t="str">
         <f ca="1">IF(OR(D56="",E56=""),"",IF(TODAY()&gt;=D56,IF(TODAY()&lt;=E56,"In progress","Passed "&amp;TODAY()-E56&amp;"d"),"In "&amp;D56-TODAY()&amp;" days"))</f>
-        <v>In 28 days</v>
+        <v>In 12 days</v>
       </c>
       <c r="I56" s="13">
-        <f ca="1">IF(H56="","",AVERAGE(I57:I70))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="14"/>
       <c r="K56" s="15"/>
@@ -6342,7 +6350,7 @@
         <v>1</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D57" s="34"/>
       <c r="E57" s="35"/>
@@ -6359,7 +6367,7 @@
         <v/>
       </c>
       <c r="I57" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" s="22"/>
       <c r="K57" s="23"/>
@@ -6424,7 +6432,7 @@
         <v>2</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D58" s="34"/>
       <c r="E58" s="35"/>
@@ -6441,7 +6449,7 @@
         <v/>
       </c>
       <c r="I58" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="22"/>
       <c r="K58" s="23"/>
@@ -6506,7 +6514,7 @@
         <v>3</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D59" s="34"/>
       <c r="E59" s="35"/>
@@ -6523,7 +6531,7 @@
         <v/>
       </c>
       <c r="I59" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="22"/>
       <c r="K59" s="22"/>
@@ -6588,7 +6596,7 @@
         <v>4</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D60" s="34"/>
       <c r="E60" s="35"/>
@@ -6605,7 +6613,7 @@
         <v/>
       </c>
       <c r="I60" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="22"/>
       <c r="K60" s="23"/>
@@ -6666,10 +6674,10 @@
     </row>
     <row r="61" spans="2:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B61" s="8" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D61" s="33">
         <v>46153</v>
@@ -6687,7 +6695,7 @@
       </c>
       <c r="H61" s="12" t="str">
         <f ca="1">IF(OR(D61="",E61=""),"",IF(TODAY()&gt;=D61,IF(TODAY()&lt;=E61,"In progress","Passed "&amp;TODAY()-E61&amp;"d"),"In "&amp;D61-TODAY()&amp;" days"))</f>
-        <v>In 34 days</v>
+        <v>In 18 days</v>
       </c>
       <c r="I61" s="13">
         <f ca="1">IF(H61="","",AVERAGE(I62:I81))</f>
@@ -6755,7 +6763,7 @@
         <v>1</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D62" s="34"/>
       <c r="E62" s="35"/>
@@ -6837,7 +6845,7 @@
         <v>2</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D63" s="34"/>
       <c r="E63" s="35"/>
@@ -6919,7 +6927,7 @@
         <v>3</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D64" s="34"/>
       <c r="E64" s="35"/>
@@ -7001,7 +7009,7 @@
         <v>4</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D65" s="34"/>
       <c r="E65" s="35"/>
@@ -7083,7 +7091,7 @@
         <v>5</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D66" s="34"/>
       <c r="E66" s="35"/>
@@ -7161,10 +7169,10 @@
     </row>
     <row r="67" spans="2:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B67" s="28" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="C67" s="29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D67" s="37">
         <v>46167</v>
@@ -7182,7 +7190,7 @@
       </c>
       <c r="H67" s="32" t="str">
         <f ca="1">IF(OR(D67="",E67=""),"",IF(TODAY()&gt;=D67,IF(TODAY()&lt;=E67,"In progress","Passed "&amp;TODAY()-E67&amp;"d"),"In "&amp;D67-TODAY()&amp;" days"))</f>
-        <v>In 48 days</v>
+        <v>In 32 days</v>
       </c>
       <c r="I67" s="13">
         <f ca="1">IF(H67="","",AVERAGE(I68:I86))</f>
@@ -7250,7 +7258,7 @@
         <v>1</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D68" s="34"/>
       <c r="E68" s="35"/>
@@ -7332,7 +7340,7 @@
         <v>2</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D69" s="34"/>
       <c r="E69" s="35"/>
@@ -7414,7 +7422,7 @@
         <v>3</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D70" s="34"/>
       <c r="E70" s="35"/>
@@ -7496,7 +7504,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D71" s="34"/>
       <c r="E71" s="35"/>
@@ -7578,7 +7586,7 @@
         <v>5</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D72" s="34"/>
       <c r="E72" s="35"/>
@@ -7660,7 +7668,7 @@
         <v>6</v>
       </c>
       <c r="C73" s="26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D73" s="34"/>
       <c r="E73" s="35"/>
@@ -7742,7 +7750,7 @@
         <v>7</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D74" s="34"/>
       <c r="E74" s="35"/>
@@ -7824,7 +7832,7 @@
         <v>8</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D75" s="34"/>
       <c r="E75" s="35"/>
@@ -7906,7 +7914,7 @@
         <v>9</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D76" s="34"/>
       <c r="E76" s="35"/>
@@ -7988,7 +7996,7 @@
         <v>10</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D77" s="34"/>
       <c r="E77" s="35"/>
@@ -8066,10 +8074,10 @@
     </row>
     <row r="78" spans="2:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B78" s="28" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C78" s="29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D78" s="37">
         <v>46182</v>
@@ -8087,7 +8095,7 @@
       </c>
       <c r="H78" s="32" t="str">
         <f ca="1">IF(OR(D78="",E78=""),"",IF(TODAY()&gt;=D78,IF(TODAY()&lt;=E78,"In progress","Passed "&amp;TODAY()-E78&amp;"d"),"In "&amp;D78-TODAY()&amp;" days"))</f>
-        <v>In 63 days</v>
+        <v>In 47 days</v>
       </c>
       <c r="I78" s="13">
         <f ca="1">IF(H78="","",AVERAGE(I79:I91))</f>
@@ -8152,10 +8160,10 @@
     </row>
     <row r="79" spans="2:65" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B79" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C79" s="29" t="s">
         <v>82</v>
-      </c>
-      <c r="C79" s="29" t="s">
-        <v>83</v>
       </c>
       <c r="D79" s="37">
         <v>46189</v>
@@ -8173,7 +8181,7 @@
       </c>
       <c r="H79" s="32" t="str">
         <f ca="1">IF(OR(D79="",E79=""),"",IF(TODAY()&gt;=D79,IF(TODAY()&lt;=E79,"In progress","Passed "&amp;TODAY()-E79&amp;"d"),"In "&amp;D79-TODAY()&amp;" days"))</f>
-        <v>In 70 days</v>
+        <v>In 54 days</v>
       </c>
       <c r="I79" s="13">
         <v>0</v>
@@ -8240,7 +8248,7 @@
         <v>1</v>
       </c>
       <c r="C80" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D80" s="34"/>
       <c r="E80" s="35"/>
@@ -8322,7 +8330,7 @@
         <v>2</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D81" s="34"/>
       <c r="E81" s="35"/>
@@ -8404,7 +8412,7 @@
         <v>3</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D82" s="34"/>
       <c r="E82" s="35"/>
@@ -8482,6 +8490,16 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="AL5:AR5"/>
+    <mergeCell ref="AS5:AY5"/>
+    <mergeCell ref="AZ5:BF5"/>
+    <mergeCell ref="BG5:BM5"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="J5:P5"/>
+    <mergeCell ref="Q5:W5"/>
+    <mergeCell ref="X5:AD5"/>
+    <mergeCell ref="AE5:AK5"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="B2:I2"/>
@@ -8496,16 +8514,6 @@
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="F5:F7"/>
-    <mergeCell ref="AL5:AR5"/>
-    <mergeCell ref="AS5:AY5"/>
-    <mergeCell ref="AZ5:BF5"/>
-    <mergeCell ref="BG5:BM5"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="J5:P5"/>
-    <mergeCell ref="Q5:W5"/>
-    <mergeCell ref="X5:AD5"/>
-    <mergeCell ref="AE5:AK5"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I82">
     <cfRule type="dataBar" priority="41">
@@ -8564,6 +8572,9 @@
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="43" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <ignoredErrors>
+    <ignoredError sqref="I51" formulaRange="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">

--- a/documents/Student Research Project - Gantt-Chart (no RACI) - Cao Đăng Khoa - UIT.xlsx
+++ b/documents/Student Research Project - Gantt-Chart (no RACI) - Cao Đăng Khoa - UIT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dkhoamac/Documents/Honours Project/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D39B7D-565C-424E-A489-B51C3840A74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99101C5-493B-FF48-A2FF-021E42C33402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="820" yWindow="620" windowWidth="26220" windowHeight="15300" xr2:uid="{7AEDD6EE-08B3-DF43-8C0E-E0ED61F366E0}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="27040" windowHeight="15260" xr2:uid="{7AEDD6EE-08B3-DF43-8C0E-E0ED61F366E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="1" r:id="rId1"/>
@@ -1183,7 +1183,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="15" fmlaLink="$I$4" horiz="1" max="100" page="0" val="53"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="15" fmlaLink="$I$4" horiz="1" max="100" page="0" val="31"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1556,6 +1556,28 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{2A266E87-D790-0F47-A964-F27CDC4D81DF}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;3c4b35d6-23c7-4ff0-86f2-89d1db71b96b&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C6657BB-24C3-8E4B-99A0-674AFBF9C3C9}">
   <sheetPr>
@@ -1633,15 +1655,15 @@
       <c r="E4" s="48"/>
       <c r="F4" s="49">
         <f ca="1">TODAY()</f>
-        <v>46135</v>
+        <v>46182</v>
       </c>
       <c r="G4" s="49"/>
       <c r="H4" s="3">
         <f ca="1">_xlfn.FLOOR.MATH(TODAY()-project_start)/7</f>
-        <v>24.714285714285715</v>
+        <v>31.428571428571427</v>
       </c>
       <c r="I4" s="3">
-        <v>53</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:65" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1671,7 +1693,7 @@
       </c>
       <c r="J5" s="58">
         <f>J6</f>
-        <v>46321</v>
+        <v>46167</v>
       </c>
       <c r="K5" s="59"/>
       <c r="L5" s="59"/>
@@ -1681,7 +1703,7 @@
       <c r="P5" s="60"/>
       <c r="Q5" s="58">
         <f>Q6</f>
-        <v>46328</v>
+        <v>46174</v>
       </c>
       <c r="R5" s="59"/>
       <c r="S5" s="59"/>
@@ -1691,7 +1713,7 @@
       <c r="W5" s="60"/>
       <c r="X5" s="58">
         <f>X6</f>
-        <v>46335</v>
+        <v>46181</v>
       </c>
       <c r="Y5" s="59"/>
       <c r="Z5" s="59"/>
@@ -1701,7 +1723,7 @@
       <c r="AD5" s="60"/>
       <c r="AE5" s="58">
         <f>AE6</f>
-        <v>46342</v>
+        <v>46188</v>
       </c>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
@@ -1711,7 +1733,7 @@
       <c r="AK5" s="60"/>
       <c r="AL5" s="58">
         <f>AL6</f>
-        <v>46349</v>
+        <v>46195</v>
       </c>
       <c r="AM5" s="59"/>
       <c r="AN5" s="59"/>
@@ -1721,7 +1743,7 @@
       <c r="AR5" s="60"/>
       <c r="AS5" s="58">
         <f>AS6</f>
-        <v>46356</v>
+        <v>46202</v>
       </c>
       <c r="AT5" s="59"/>
       <c r="AU5" s="59"/>
@@ -1731,7 +1753,7 @@
       <c r="AY5" s="60"/>
       <c r="AZ5" s="58">
         <f>AZ6</f>
-        <v>46363</v>
+        <v>46209</v>
       </c>
       <c r="BA5" s="59"/>
       <c r="BB5" s="59"/>
@@ -1741,7 +1763,7 @@
       <c r="BF5" s="60"/>
       <c r="BG5" s="58">
         <f>BG6</f>
-        <v>46370</v>
+        <v>46216</v>
       </c>
       <c r="BH5" s="59"/>
       <c r="BI5" s="59"/>
@@ -1761,227 +1783,227 @@
       <c r="I6" s="61"/>
       <c r="J6" s="4">
         <f>$B$4-WEEKDAY(project_start,3)+(display_week-1)*7</f>
-        <v>46321</v>
+        <v>46167</v>
       </c>
       <c r="K6" s="5">
         <f>J6+1</f>
-        <v>46322</v>
+        <v>46168</v>
       </c>
       <c r="L6" s="5">
         <f t="shared" ref="L6:Q6" si="0">K6+1</f>
-        <v>46323</v>
+        <v>46169</v>
       </c>
       <c r="M6" s="5">
         <f t="shared" si="0"/>
-        <v>46324</v>
+        <v>46170</v>
       </c>
       <c r="N6" s="5">
         <f t="shared" si="0"/>
-        <v>46325</v>
+        <v>46171</v>
       </c>
       <c r="O6" s="5">
         <f t="shared" si="0"/>
-        <v>46326</v>
+        <v>46172</v>
       </c>
       <c r="P6" s="5">
         <f t="shared" si="0"/>
-        <v>46327</v>
+        <v>46173</v>
       </c>
       <c r="Q6" s="5">
         <f t="shared" si="0"/>
-        <v>46328</v>
+        <v>46174</v>
       </c>
       <c r="R6" s="5">
         <f>Q6+1</f>
-        <v>46329</v>
+        <v>46175</v>
       </c>
       <c r="S6" s="5">
         <f t="shared" ref="S6:X6" si="1">R6+1</f>
-        <v>46330</v>
+        <v>46176</v>
       </c>
       <c r="T6" s="5">
         <f t="shared" si="1"/>
-        <v>46331</v>
+        <v>46177</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="1"/>
-        <v>46332</v>
+        <v>46178</v>
       </c>
       <c r="V6" s="5">
         <f t="shared" si="1"/>
-        <v>46333</v>
+        <v>46179</v>
       </c>
       <c r="W6" s="5">
         <f t="shared" si="1"/>
-        <v>46334</v>
+        <v>46180</v>
       </c>
       <c r="X6" s="5">
         <f t="shared" si="1"/>
-        <v>46335</v>
+        <v>46181</v>
       </c>
       <c r="Y6" s="5">
         <f>X6+1</f>
-        <v>46336</v>
+        <v>46182</v>
       </c>
       <c r="Z6" s="5">
         <f t="shared" ref="Z6:AE6" si="2">Y6+1</f>
-        <v>46337</v>
+        <v>46183</v>
       </c>
       <c r="AA6" s="5">
         <f t="shared" si="2"/>
-        <v>46338</v>
+        <v>46184</v>
       </c>
       <c r="AB6" s="5">
         <f t="shared" si="2"/>
-        <v>46339</v>
+        <v>46185</v>
       </c>
       <c r="AC6" s="5">
         <f t="shared" si="2"/>
-        <v>46340</v>
+        <v>46186</v>
       </c>
       <c r="AD6" s="5">
         <f t="shared" si="2"/>
-        <v>46341</v>
+        <v>46187</v>
       </c>
       <c r="AE6" s="5">
         <f t="shared" si="2"/>
-        <v>46342</v>
+        <v>46188</v>
       </c>
       <c r="AF6" s="5">
         <f>AE6+1</f>
-        <v>46343</v>
+        <v>46189</v>
       </c>
       <c r="AG6" s="5">
         <f t="shared" ref="AG6:BM6" si="3">AF6+1</f>
-        <v>46344</v>
+        <v>46190</v>
       </c>
       <c r="AH6" s="5">
         <f t="shared" si="3"/>
-        <v>46345</v>
+        <v>46191</v>
       </c>
       <c r="AI6" s="5">
         <f t="shared" si="3"/>
-        <v>46346</v>
+        <v>46192</v>
       </c>
       <c r="AJ6" s="5">
         <f t="shared" si="3"/>
-        <v>46347</v>
+        <v>46193</v>
       </c>
       <c r="AK6" s="5">
         <f t="shared" si="3"/>
-        <v>46348</v>
+        <v>46194</v>
       </c>
       <c r="AL6" s="5">
         <f t="shared" si="3"/>
-        <v>46349</v>
+        <v>46195</v>
       </c>
       <c r="AM6" s="5">
         <f t="shared" si="3"/>
-        <v>46350</v>
+        <v>46196</v>
       </c>
       <c r="AN6" s="5">
         <f t="shared" si="3"/>
-        <v>46351</v>
+        <v>46197</v>
       </c>
       <c r="AO6" s="5">
         <f t="shared" si="3"/>
-        <v>46352</v>
+        <v>46198</v>
       </c>
       <c r="AP6" s="5">
         <f t="shared" si="3"/>
-        <v>46353</v>
+        <v>46199</v>
       </c>
       <c r="AQ6" s="5">
         <f t="shared" si="3"/>
-        <v>46354</v>
+        <v>46200</v>
       </c>
       <c r="AR6" s="5">
         <f t="shared" si="3"/>
-        <v>46355</v>
+        <v>46201</v>
       </c>
       <c r="AS6" s="5">
         <f t="shared" si="3"/>
-        <v>46356</v>
+        <v>46202</v>
       </c>
       <c r="AT6" s="5">
         <f t="shared" si="3"/>
-        <v>46357</v>
+        <v>46203</v>
       </c>
       <c r="AU6" s="5">
         <f t="shared" si="3"/>
-        <v>46358</v>
+        <v>46204</v>
       </c>
       <c r="AV6" s="5">
         <f t="shared" si="3"/>
-        <v>46359</v>
+        <v>46205</v>
       </c>
       <c r="AW6" s="5">
         <f t="shared" si="3"/>
-        <v>46360</v>
+        <v>46206</v>
       </c>
       <c r="AX6" s="5">
         <f t="shared" si="3"/>
-        <v>46361</v>
+        <v>46207</v>
       </c>
       <c r="AY6" s="5">
         <f t="shared" si="3"/>
-        <v>46362</v>
+        <v>46208</v>
       </c>
       <c r="AZ6" s="5">
         <f t="shared" si="3"/>
-        <v>46363</v>
+        <v>46209</v>
       </c>
       <c r="BA6" s="5">
         <f t="shared" si="3"/>
-        <v>46364</v>
+        <v>46210</v>
       </c>
       <c r="BB6" s="5">
         <f t="shared" si="3"/>
-        <v>46365</v>
+        <v>46211</v>
       </c>
       <c r="BC6" s="5">
         <f t="shared" si="3"/>
-        <v>46366</v>
+        <v>46212</v>
       </c>
       <c r="BD6" s="5">
         <f t="shared" si="3"/>
-        <v>46367</v>
+        <v>46213</v>
       </c>
       <c r="BE6" s="5">
         <f t="shared" si="3"/>
-        <v>46368</v>
+        <v>46214</v>
       </c>
       <c r="BF6" s="5">
         <f t="shared" si="3"/>
-        <v>46369</v>
+        <v>46215</v>
       </c>
       <c r="BG6" s="5">
         <f t="shared" si="3"/>
-        <v>46370</v>
+        <v>46216</v>
       </c>
       <c r="BH6" s="5">
         <f t="shared" si="3"/>
-        <v>46371</v>
+        <v>46217</v>
       </c>
       <c r="BI6" s="5">
         <f t="shared" si="3"/>
-        <v>46372</v>
+        <v>46218</v>
       </c>
       <c r="BJ6" s="5">
         <f t="shared" si="3"/>
-        <v>46373</v>
+        <v>46219</v>
       </c>
       <c r="BK6" s="5">
         <f t="shared" si="3"/>
-        <v>46374</v>
+        <v>46220</v>
       </c>
       <c r="BL6" s="5">
         <f t="shared" si="3"/>
-        <v>46375</v>
+        <v>46221</v>
       </c>
       <c r="BM6" s="5">
         <f t="shared" si="3"/>
-        <v>46376</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="7" spans="2:65" ht="20" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -2241,7 +2263,7 @@
       </c>
       <c r="H8" s="12" t="str">
         <f t="shared" ref="H8:H65" ca="1" si="12">IF(OR(D8="",E8=""),"",IF(TODAY()&gt;=D8,IF(TODAY()&lt;=E8,"In progress","Passed "&amp;TODAY()-E8&amp;"d"),"In "&amp;D8-TODAY()&amp;" days"))</f>
-        <v>Passed 164d</v>
+        <v>Passed 211d</v>
       </c>
       <c r="I8" s="13">
         <f ca="1">IF(H8="","",AVERAGE(I9:I13))</f>
@@ -2327,7 +2349,7 @@
       </c>
       <c r="H9" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 164d</v>
+        <v>Passed 211d</v>
       </c>
       <c r="I9" s="21">
         <v>1</v>
@@ -2413,7 +2435,7 @@
       </c>
       <c r="H10" s="20" t="str">
         <f t="shared" ref="H10:H11" ca="1" si="17">IF(OR(D10="",E10=""),"",IF(TODAY()&gt;=D10,IF(TODAY()&lt;=E10,"In progress","Passed "&amp;TODAY()-E10&amp;"d"),"In "&amp;D10-TODAY()&amp;" days"))</f>
-        <v>Passed 164d</v>
+        <v>Passed 211d</v>
       </c>
       <c r="I10" s="21">
         <v>1</v>
@@ -2499,7 +2521,7 @@
       </c>
       <c r="H11" s="20" t="str">
         <f t="shared" ca="1" si="17"/>
-        <v>Passed 164d</v>
+        <v>Passed 211d</v>
       </c>
       <c r="I11" s="21">
         <v>1</v>
@@ -2585,7 +2607,7 @@
       </c>
       <c r="H12" s="20" t="str">
         <f ca="1">IF(OR(D12="",E12=""),"",IF(TODAY()&gt;=D12,IF(TODAY()&lt;=E12,"In progress","Passed "&amp;TODAY()-E12&amp;"d"),"In "&amp;D12-TODAY()&amp;" days"))</f>
-        <v>Passed 164d</v>
+        <v>Passed 211d</v>
       </c>
       <c r="I12" s="21">
         <v>1</v>
@@ -2671,7 +2693,7 @@
       </c>
       <c r="H13" s="20" t="str">
         <f t="shared" ref="H13" ca="1" si="21">IF(OR(D13="",E13=""),"",IF(TODAY()&gt;=D13,IF(TODAY()&lt;=E13,"In progress","Passed "&amp;TODAY()-E13&amp;"d"),"In "&amp;D13-TODAY()&amp;" days"))</f>
-        <v>Passed 150d</v>
+        <v>Passed 197d</v>
       </c>
       <c r="I13" s="21">
         <v>1</v>
@@ -2756,7 +2778,7 @@
       </c>
       <c r="H14" s="12" t="str">
         <f ca="1">IF(OR(D14="",E14=""),"",IF(TODAY()&gt;=D14,IF(TODAY()&lt;=E14,"In progress","Passed "&amp;TODAY()-E14&amp;"d"),"In "&amp;D14-TODAY()&amp;" days"))</f>
-        <v>Passed 144d</v>
+        <v>Passed 191d</v>
       </c>
       <c r="I14" s="13">
         <f ca="1">IF(H14="","",AVERAGE(I15:I19))</f>
@@ -2842,7 +2864,7 @@
       </c>
       <c r="H15" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 144d</v>
+        <v>Passed 191d</v>
       </c>
       <c r="I15" s="21">
         <v>1</v>
@@ -2927,7 +2949,7 @@
       </c>
       <c r="H16" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 144d</v>
+        <v>Passed 191d</v>
       </c>
       <c r="I16" s="21">
         <v>1</v>
@@ -3012,7 +3034,7 @@
       </c>
       <c r="H17" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 144d</v>
+        <v>Passed 191d</v>
       </c>
       <c r="I17" s="21">
         <v>1</v>
@@ -3097,7 +3119,7 @@
       </c>
       <c r="H18" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 144d</v>
+        <v>Passed 191d</v>
       </c>
       <c r="I18" s="21">
         <v>1</v>
@@ -3182,7 +3204,7 @@
       </c>
       <c r="H19" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 144d</v>
+        <v>Passed 191d</v>
       </c>
       <c r="I19" s="21">
         <v>1</v>
@@ -3267,7 +3289,7 @@
       </c>
       <c r="H20" s="12" t="str">
         <f t="shared" ref="H20:H24" ca="1" si="22">IF(OR(D20="",E20=""),"",IF(TODAY()&gt;=D20,IF(TODAY()&lt;=E20,"In progress","Passed "&amp;TODAY()-E20&amp;"d"),"In "&amp;D20-TODAY()&amp;" days"))</f>
-        <v>Passed 137d</v>
+        <v>Passed 184d</v>
       </c>
       <c r="I20" s="13">
         <f ca="1">IF(H20="","",AVERAGE(I21:I24))</f>
@@ -3353,7 +3375,7 @@
       </c>
       <c r="H21" s="20" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>Passed 137d</v>
+        <v>Passed 184d</v>
       </c>
       <c r="I21" s="21">
         <v>1</v>
@@ -3439,7 +3461,7 @@
       </c>
       <c r="H22" s="20" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>Passed 137d</v>
+        <v>Passed 184d</v>
       </c>
       <c r="I22" s="21">
         <v>1</v>
@@ -3525,7 +3547,7 @@
       </c>
       <c r="H23" s="20" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>Passed 137d</v>
+        <v>Passed 184d</v>
       </c>
       <c r="I23" s="21">
         <v>1</v>
@@ -3611,7 +3633,7 @@
       </c>
       <c r="H24" s="20" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>Passed 137d</v>
+        <v>Passed 184d</v>
       </c>
       <c r="I24" s="21">
         <v>1</v>
@@ -3696,7 +3718,7 @@
       </c>
       <c r="H25" s="32" t="str">
         <f ca="1">IF(OR(D25="",E25=""),"",IF(TODAY()&gt;=D25,IF(TODAY()&lt;=E25,"In progress","Passed "&amp;TODAY()-E25&amp;"d"),"In "&amp;D25-TODAY()&amp;" days"))</f>
-        <v>Passed 136d</v>
+        <v>Passed 183d</v>
       </c>
       <c r="I25" s="13">
         <f ca="1">IF(H25="","",AVERAGE(I26:I26))</f>
@@ -3782,7 +3804,7 @@
       </c>
       <c r="H26" s="20" t="str">
         <f t="shared" ref="H26" ca="1" si="27">IF(OR(D26="",E26=""),"",IF(TODAY()&gt;=D26,IF(TODAY()&lt;=E26,"In progress","Passed "&amp;TODAY()-E26&amp;"d"),"In "&amp;D26-TODAY()&amp;" days"))</f>
-        <v>Passed 136d</v>
+        <v>Passed 183d</v>
       </c>
       <c r="I26" s="21">
         <v>1</v>
@@ -3867,7 +3889,7 @@
       </c>
       <c r="H27" s="12" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 51d</v>
+        <v>Passed 98d</v>
       </c>
       <c r="I27" s="13">
         <f ca="1">IF(H27="","",AVERAGE(I28:I31))</f>
@@ -3953,7 +3975,7 @@
       </c>
       <c r="H28" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 51d</v>
+        <v>Passed 98d</v>
       </c>
       <c r="I28" s="21">
         <v>1</v>
@@ -4039,7 +4061,7 @@
       </c>
       <c r="H29" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 51d</v>
+        <v>Passed 98d</v>
       </c>
       <c r="I29" s="21">
         <v>1</v>
@@ -4125,7 +4147,7 @@
       </c>
       <c r="H30" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 51d</v>
+        <v>Passed 98d</v>
       </c>
       <c r="I30" s="21">
         <v>1</v>
@@ -4211,7 +4233,7 @@
       </c>
       <c r="H31" s="20" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>Passed 51d</v>
+        <v>Passed 98d</v>
       </c>
       <c r="I31" s="21">
         <v>1</v>
@@ -4296,7 +4318,7 @@
       </c>
       <c r="H32" s="32" t="str">
         <f ca="1">IF(OR(D32="",E32=""),"",IF(TODAY()&gt;=D32,IF(TODAY()&lt;=E32,"In progress","Passed "&amp;TODAY()-E32&amp;"d"),"In "&amp;D32-TODAY()&amp;" days"))</f>
-        <v>Passed 101d</v>
+        <v>Passed 148d</v>
       </c>
       <c r="I32" s="13">
         <f ca="1">IF(H32="","",AVERAGE(I33:I33))</f>
@@ -4382,7 +4404,7 @@
       </c>
       <c r="H33" s="20" t="str">
         <f t="shared" ref="H33" ca="1" si="30">IF(OR(D33="",E33=""),"",IF(TODAY()&gt;=D33,IF(TODAY()&lt;=E33,"In progress","Passed "&amp;TODAY()-E33&amp;"d"),"In "&amp;D33-TODAY()&amp;" days"))</f>
-        <v>Passed 101d</v>
+        <v>Passed 148d</v>
       </c>
       <c r="I33" s="21">
         <v>1</v>
@@ -4467,7 +4489,7 @@
       </c>
       <c r="H34" s="12" t="str">
         <f ca="1">IF(OR(D34="",E34=""),"",IF(TODAY()&gt;=D34,IF(TODAY()&lt;=E34,"In progress","Passed "&amp;TODAY()-E34&amp;"d"),"In "&amp;D34-TODAY()&amp;" days"))</f>
-        <v>Passed 25d</v>
+        <v>Passed 72d</v>
       </c>
       <c r="I34" s="13">
         <f ca="1">IF(H34="","",AVERAGE(I35:I39))</f>
@@ -4962,11 +4984,11 @@
       </c>
       <c r="H40" s="12" t="str">
         <f ca="1">IF(OR(D40="",E40=""),"",IF(TODAY()&gt;=D40,IF(TODAY()&lt;=E40,"In progress","Passed "&amp;TODAY()-E40&amp;"d"),"In "&amp;D40-TODAY()&amp;" days"))</f>
-        <v>Passed 10d</v>
+        <v>Passed 57d</v>
       </c>
       <c r="I40" s="13">
         <f ca="1">IF(H40="","",AVERAGE(I41:I45))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="14"/>
       <c r="K40" s="15"/>
@@ -5047,7 +5069,7 @@
         <v/>
       </c>
       <c r="I41" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="22"/>
       <c r="K41" s="23"/>
@@ -5129,7 +5151,7 @@
         <v/>
       </c>
       <c r="I42" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="22"/>
       <c r="K42" s="23"/>
@@ -5211,7 +5233,7 @@
         <v/>
       </c>
       <c r="I43" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="22"/>
       <c r="K43" s="23"/>
@@ -5293,7 +5315,7 @@
         <v/>
       </c>
       <c r="I44" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="22"/>
       <c r="K44" s="23"/>
@@ -5375,7 +5397,7 @@
         <v/>
       </c>
       <c r="I45" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="22"/>
       <c r="K45" s="23"/>
@@ -5457,7 +5479,7 @@
       </c>
       <c r="H46" s="32" t="str">
         <f ca="1">IF(OR(D46="",E46=""),"",IF(TODAY()&gt;=D46,IF(TODAY()&lt;=E46,"In progress","Passed "&amp;TODAY()-E46&amp;"d"),"In "&amp;D46-TODAY()&amp;" days"))</f>
-        <v>Passed 17d</v>
+        <v>Passed 64d</v>
       </c>
       <c r="I46" s="13">
         <f ca="1">IF(H46="","",AVERAGE(I47:I50))</f>
@@ -5870,7 +5892,7 @@
       </c>
       <c r="H51" s="12" t="str">
         <f ca="1">IF(OR(D51="",E51=""),"",IF(TODAY()&gt;=D51,IF(TODAY()&lt;=E51,"In progress","Passed "&amp;TODAY()-E51&amp;"d"),"In "&amp;D51-TODAY()&amp;" days"))</f>
-        <v>In progress</v>
+        <v>Passed 36d</v>
       </c>
       <c r="I51" s="13">
         <f ca="1">IF(H51="","",AVERAGE(I52:I55))</f>
@@ -6283,7 +6305,7 @@
       </c>
       <c r="H56" s="12" t="str">
         <f ca="1">IF(OR(D56="",E56=""),"",IF(TODAY()&gt;=D56,IF(TODAY()&lt;=E56,"In progress","Passed "&amp;TODAY()-E56&amp;"d"),"In "&amp;D56-TODAY()&amp;" days"))</f>
-        <v>In 12 days</v>
+        <v>Passed 30d</v>
       </c>
       <c r="I56" s="13">
         <v>1</v>
@@ -6695,11 +6717,10 @@
       </c>
       <c r="H61" s="12" t="str">
         <f ca="1">IF(OR(D61="",E61=""),"",IF(TODAY()&gt;=D61,IF(TODAY()&lt;=E61,"In progress","Passed "&amp;TODAY()-E61&amp;"d"),"In "&amp;D61-TODAY()&amp;" days"))</f>
-        <v>In 18 days</v>
+        <v>Passed 16d</v>
       </c>
       <c r="I61" s="13">
-        <f ca="1">IF(H61="","",AVERAGE(I62:I81))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" s="14"/>
       <c r="K61" s="15"/>
@@ -6780,7 +6801,7 @@
         <v/>
       </c>
       <c r="I62" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="22"/>
       <c r="K62" s="23"/>
@@ -6862,7 +6883,7 @@
         <v/>
       </c>
       <c r="I63" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" s="22"/>
       <c r="K63" s="23"/>
@@ -6944,7 +6965,7 @@
         <v/>
       </c>
       <c r="I64" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" s="22"/>
       <c r="K64" s="23"/>
@@ -7026,7 +7047,7 @@
         <v/>
       </c>
       <c r="I65" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" s="22"/>
       <c r="K65" s="23"/>
@@ -7108,7 +7129,7 @@
         <v/>
       </c>
       <c r="I66" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" s="22"/>
       <c r="K66" s="23"/>
@@ -7190,11 +7211,11 @@
       </c>
       <c r="H67" s="32" t="str">
         <f ca="1">IF(OR(D67="",E67=""),"",IF(TODAY()&gt;=D67,IF(TODAY()&lt;=E67,"In progress","Passed "&amp;TODAY()-E67&amp;"d"),"In "&amp;D67-TODAY()&amp;" days"))</f>
-        <v>In 32 days</v>
+        <v>Passed 1d</v>
       </c>
       <c r="I67" s="13">
-        <f ca="1">IF(H67="","",AVERAGE(I68:I86))</f>
-        <v>0</v>
+        <f ca="1">IF(H67="","",AVERAGE(I68:I77))</f>
+        <v>1</v>
       </c>
       <c r="J67" s="14"/>
       <c r="K67" s="15"/>
@@ -7275,7 +7296,7 @@
         <v/>
       </c>
       <c r="I68" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" s="22"/>
       <c r="K68" s="23"/>
@@ -7357,7 +7378,7 @@
         <v/>
       </c>
       <c r="I69" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" s="22"/>
       <c r="K69" s="23"/>
@@ -7439,7 +7460,7 @@
         <v/>
       </c>
       <c r="I70" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="22"/>
       <c r="K70" s="23"/>
@@ -7521,7 +7542,7 @@
         <v/>
       </c>
       <c r="I71" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" s="22"/>
       <c r="K71" s="23"/>
@@ -7603,7 +7624,7 @@
         <v/>
       </c>
       <c r="I72" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" s="22"/>
       <c r="K72" s="23"/>
@@ -7685,7 +7706,7 @@
         <v/>
       </c>
       <c r="I73" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" s="22"/>
       <c r="K73" s="23"/>
@@ -7767,7 +7788,7 @@
         <v/>
       </c>
       <c r="I74" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" s="22"/>
       <c r="K74" s="23"/>
@@ -7849,7 +7870,7 @@
         <v/>
       </c>
       <c r="I75" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="22"/>
       <c r="K75" s="23"/>
@@ -7931,7 +7952,7 @@
         <v/>
       </c>
       <c r="I76" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" s="22"/>
       <c r="K76" s="23"/>
@@ -8013,7 +8034,7 @@
         <v/>
       </c>
       <c r="I77" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" s="22"/>
       <c r="K77" s="23"/>
@@ -8095,7 +8116,7 @@
       </c>
       <c r="H78" s="32" t="str">
         <f ca="1">IF(OR(D78="",E78=""),"",IF(TODAY()&gt;=D78,IF(TODAY()&lt;=E78,"In progress","Passed "&amp;TODAY()-E78&amp;"d"),"In "&amp;D78-TODAY()&amp;" days"))</f>
-        <v>In 47 days</v>
+        <v>In progress</v>
       </c>
       <c r="I78" s="13">
         <f ca="1">IF(H78="","",AVERAGE(I79:I91))</f>
@@ -8181,7 +8202,7 @@
       </c>
       <c r="H79" s="32" t="str">
         <f ca="1">IF(OR(D79="",E79=""),"",IF(TODAY()&gt;=D79,IF(TODAY()&lt;=E79,"In progress","Passed "&amp;TODAY()-E79&amp;"d"),"In "&amp;D79-TODAY()&amp;" days"))</f>
-        <v>In 54 days</v>
+        <v>In 7 days</v>
       </c>
       <c r="I79" s="13">
         <v>0</v>
